--- a/registration_forms/006_aec_workflow_registration_form--registration_forms.xlsx
+++ b/registration_forms/006_aec_workflow_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -969,8 +969,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -998,12 +998,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'architecture',_'value':_'architecture'}</t>
+          <t>architecture</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Architecture', 'value': 'architecture'}</t>
+          <t>Architecture</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'structural_engineering',_'value':_'structural_engineering'}</t>
+          <t>structural_engineering</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Structural Engineering', 'value': 'structural_engineering'}</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'mep_engineering',_'value':_'mep_engineering'}</t>
+          <t>mep_engineering</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'MEP Engineering', 'value': 'mep_engineering'}</t>
+          <t>MEP Engineering</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'civil_engineering',_'value':_'civil_engineering'}</t>
+          <t>civil_engineering</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Civil Engineering', 'value': 'civil_engineering'}</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'general_contracting',_'value':_'general_contracting'}</t>
+          <t>general_contracting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'General Contracting', 'value': 'general_contracting'}</t>
+          <t>General Contracting</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'project_management',_'value':_'project_management'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Project Management', 'value': 'project_management'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'interior_design',_'value':_'interior_design'}</t>
+          <t>interior_design</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Interior Design', 'value': 'interior_design'}</t>
+          <t>Interior Design</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'autodesk_revit',_'value':_'revit'}</t>
+          <t>autodesk_revit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Autodesk Revit', 'value': 'revit'}</t>
+          <t>Autodesk Revit</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'autocad',_'value':_'autocad'}</t>
+          <t>autocad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'AutoCAD', 'value': 'autocad'}</t>
+          <t>AutoCAD</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'rhino_/_grasshopper',_'value':_'rhino'}</t>
+          <t>rhino_/_grasshopper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Rhino / Grasshopper', 'value': 'rhino'}</t>
+          <t>Rhino / Grasshopper</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'archicad',_'value':_'archicad'}</t>
+          <t>archicad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'ArchiCAD', 'value': 'archicad'}</t>
+          <t>ArchiCAD</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'bluebeam_revu',_'value':_'bluebeam'}</t>
+          <t>bluebeam_revu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Bluebeam Revu', 'value': 'bluebeam'}</t>
+          <t>Bluebeam Revu</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'navisworks',_'value':_'navisworks'}</t>
+          <t>navisworks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Navisworks', 'value': 'navisworks'}</t>
+          <t>Navisworks</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'bentley_systems',_'value':_'bentley'}</t>
+          <t>bentley_systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Bentley Systems', 'value': 'bentley'}</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'bim_coordination',_'value':_'bim_coordination'}</t>
+          <t>bim_coordination</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'BIM Coordination', 'value': 'bim_coordination'}</t>
+          <t>BIM Coordination</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'generative_design',_'value':_'generative_design'}</t>
+          <t>generative_design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Generative Design', 'value': 'generative_design'}</t>
+          <t>Generative Design</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'sustainable_design_/_analysis',_'value':_'sustainability'}</t>
+          <t>sustainable_design_/_analysis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Sustainable Design / Analysis', 'value': 'sustainability'}</t>
+          <t>Sustainable Design / Analysis</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'vdc_(virtual_design_and_construction)',_'value':_'vdc'}</t>
+          <t>vdc_(virtual_design_and_construction)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'VDC (Virtual Design and Construction)', 'value': 'vdc'}</t>
+          <t>VDC (Virtual Design and Construction)</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'digital_twin_technology',_'value':_'digital_twin'}</t>
+          <t>digital_twin_technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Digital Twin Technology', 'value': 'digital_twin'}</t>
+          <t>Digital Twin Technology</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'cloud_collaboration',_'value':_'cloud_collab'}</t>
+          <t>cloud_collaboration</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Cloud Collaboration', 'value': 'cloud_collab'}</t>
+          <t>Cloud Collaboration</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'beginner_(learning)',_'value':_'beginner'}</t>
+          <t>beginner_(learning)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner (Learning)', 'value': 'beginner'}</t>
+          <t>Beginner (Learning)</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate_(regular_use)',_'value':_'intermediate'}</t>
+          <t>intermediate_(regular_use)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate (Regular use)', 'value': 'intermediate'}</t>
+          <t>Intermediate (Regular use)</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_(workflow_optimization)',_'value':_'advanced'}</t>
+          <t>advanced_(workflow_optimization)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced (Workflow optimization)', 'value': 'advanced'}</t>
+          <t>Advanced (Workflow optimization)</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'expert_(strategic_implementation)',_'value':_'expert'}</t>
+          <t>expert_(strategic_implementation)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Expert (Strategic implementation)', 'value': 'expert'}</t>
+          <t>Expert (Strategic implementation)</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'automation_with_dynamo',_'value':_'dynamo'}</t>
+          <t>automation_with_dynamo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Automation with Dynamo', 'value': 'dynamo'}</t>
+          <t>Automation with Dynamo</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'clash_detection_best_practices',_'value':_'clash_detection'}</t>
+          <t>clash_detection_best_practices</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Clash Detection Best Practices', 'value': 'clash_detection'}</t>
+          <t>Clash Detection Best Practices</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'reality_capture_and_lidar',_'value':_'lidar'}</t>
+          <t>reality_capture_and_lidar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Reality Capture and LiDAR', 'value': 'lidar'}</t>
+          <t>Reality Capture and LiDAR</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'managing_large-scale_bim_projects',_'value':_'large_scale_bim'}</t>
+          <t>managing_large-scale_bim_projects</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Managing Large-Scale BIM Projects', 'value': 'large_scale_bim'}</t>
+          <t>Managing Large-Scale BIM Projects</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'confirmed',_'value':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Confirmed', 'value': 'confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
